--- a/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260824.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0050/ETF_Investment_Portfolio_20260824.xlsx
@@ -931,17 +931,17 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>61,476,368</t>
+          <t>544,744,779</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -953,17 +953,17 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>544,744,779</t>
+          <t>61,476,368</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
@@ -1129,17 +1129,17 @@
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>275,064,288</t>
+          <t>45,504,287</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,17 +1151,17 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>45,504,287</t>
+          <t>275,064,288</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
@@ -1569,17 +1569,17 @@
     <row r="65">
       <c r="A65" s="3" t="inlineStr">
         <is>
-          <t>2449</t>
+          <t>5880</t>
         </is>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>京元電子</t>
+          <t>合庫金</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>26,570,865</t>
+          <t>250,537,251</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
@@ -1591,17 +1591,17 @@
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>5880</t>
+          <t>2449</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>合庫金</t>
+          <t>京元電子</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>250,537,251</t>
+          <t>26,570,865</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
